--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -31706,7 +31706,7 @@
         <v>610184</v>
       </c>
       <c r="C1363" t="n">
-        <v>4.40999984741211</v>
+        <v>4.44000005722046</v>
       </c>
       <c r="D1363" t="n">
         <v>4.15999984741211</v>
@@ -31718,6 +31718,29 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1363" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1364" t="n">
+        <v>535609</v>
+      </c>
+      <c r="C1364" t="n">
+        <v>4.38500022888184</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>4.22499990463257</v>
+      </c>
+      <c r="G1364" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -31744,6 +31744,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1365">
+      <c r="A1365" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1365" t="n">
+        <v>571579</v>
+      </c>
+      <c r="C1365" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>4.13000011444092</v>
+      </c>
+      <c r="G1365" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -31767,6 +31767,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1366">
+      <c r="A1366" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1366" t="n">
+        <v>506429</v>
+      </c>
+      <c r="C1366" t="n">
+        <v>4.24499988555908</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>4.01000022888184</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>4.10500001907349</v>
+      </c>
+      <c r="G1366" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -31790,6 +31790,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1367">
+      <c r="A1367" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1367" t="n">
+        <v>458391</v>
+      </c>
+      <c r="C1367" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>4.16499996185303</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>4.29500007629395</v>
+      </c>
+      <c r="G1367" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -31631,22 +31631,22 @@
     </row>
     <row r="1360">
       <c r="A1360" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1360" t="n">
-        <v>1439360</v>
+        <v>876274</v>
       </c>
       <c r="C1360" t="n">
-        <v>4.07999992370605</v>
+        <v>3.54999995231628</v>
       </c>
       <c r="D1360" t="n">
-        <v>3.5</v>
+        <v>3.3199999332428</v>
       </c>
       <c r="E1360" t="n">
-        <v>3.53999996185303</v>
+        <v>3.34999990463257</v>
       </c>
       <c r="F1360" t="n">
-        <v>4.0149998664856</v>
+        <v>3.51999998092651</v>
       </c>
       <c r="G1360" t="s">
         <v>7</v>
@@ -31654,22 +31654,22 @@
     </row>
     <row r="1361">
       <c r="A1361" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1361" t="n">
-        <v>1592877</v>
+        <v>1439360</v>
       </c>
       <c r="C1361" t="n">
-        <v>4.28499984741211</v>
+        <v>4.07999992370605</v>
       </c>
       <c r="D1361" t="n">
-        <v>3.85999989509583</v>
+        <v>3.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>3.97000002861023</v>
+        <v>3.53999996185303</v>
       </c>
       <c r="F1361" t="n">
-        <v>4.07000017166138</v>
+        <v>4.0149998664856</v>
       </c>
       <c r="G1361" t="s">
         <v>7</v>
@@ -31677,22 +31677,22 @@
     </row>
     <row r="1362">
       <c r="A1362" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1362" t="n">
-        <v>677153</v>
+        <v>1592877</v>
       </c>
       <c r="C1362" t="n">
-        <v>4.29500007629395</v>
+        <v>4.28499984741211</v>
       </c>
       <c r="D1362" t="n">
-        <v>3.96000003814697</v>
+        <v>3.85999989509583</v>
       </c>
       <c r="E1362" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="F1362" t="n">
         <v>4.07000017166138</v>
-      </c>
-      <c r="F1362" t="n">
-        <v>4.2649998664856</v>
       </c>
       <c r="G1362" t="s">
         <v>7</v>
@@ -31700,22 +31700,22 @@
     </row>
     <row r="1363">
       <c r="A1363" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1363" t="n">
-        <v>610184</v>
+        <v>677153</v>
       </c>
       <c r="C1363" t="n">
-        <v>4.44000005722046</v>
+        <v>4.29500007629395</v>
       </c>
       <c r="D1363" t="n">
-        <v>4.15999984741211</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="E1363" t="n">
-        <v>4.27500009536743</v>
+        <v>4.07000017166138</v>
       </c>
       <c r="F1363" t="n">
-        <v>4.44000005722046</v>
+        <v>4.2649998664856</v>
       </c>
       <c r="G1363" t="s">
         <v>7</v>
@@ -31723,22 +31723,22 @@
     </row>
     <row r="1364">
       <c r="A1364" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1364" t="n">
-        <v>535609</v>
+        <v>610184</v>
       </c>
       <c r="C1364" t="n">
-        <v>4.38500022888184</v>
+        <v>4.44000005722046</v>
       </c>
       <c r="D1364" t="n">
         <v>4.15999984741211</v>
       </c>
       <c r="E1364" t="n">
-        <v>4.32999992370605</v>
+        <v>4.27500009536743</v>
       </c>
       <c r="F1364" t="n">
-        <v>4.22499990463257</v>
+        <v>4.44000005722046</v>
       </c>
       <c r="G1364" t="s">
         <v>7</v>
@@ -31746,22 +31746,22 @@
     </row>
     <row r="1365">
       <c r="A1365" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1365" t="n">
-        <v>571579</v>
+        <v>535609</v>
       </c>
       <c r="C1365" t="n">
-        <v>4.34999990463257</v>
+        <v>4.38500022888184</v>
       </c>
       <c r="D1365" t="n">
-        <v>4.1100001335144</v>
+        <v>4.15999984741211</v>
       </c>
       <c r="E1365" t="n">
-        <v>4.23000001907349</v>
+        <v>4.32999992370605</v>
       </c>
       <c r="F1365" t="n">
-        <v>4.13000011444092</v>
+        <v>4.22499990463257</v>
       </c>
       <c r="G1365" t="s">
         <v>7</v>
@@ -31769,22 +31769,22 @@
     </row>
     <row r="1366">
       <c r="A1366" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1366" t="n">
-        <v>506429</v>
+        <v>571579</v>
       </c>
       <c r="C1366" t="n">
-        <v>4.24499988555908</v>
+        <v>4.34999990463257</v>
       </c>
       <c r="D1366" t="n">
-        <v>4.01000022888184</v>
+        <v>4.1100001335144</v>
       </c>
       <c r="E1366" t="n">
-        <v>4.15000009536743</v>
+        <v>4.23000001907349</v>
       </c>
       <c r="F1366" t="n">
-        <v>4.10500001907349</v>
+        <v>4.13000011444092</v>
       </c>
       <c r="G1366" t="s">
         <v>7</v>
@@ -31792,24 +31792,47 @@
     </row>
     <row r="1367">
       <c r="A1367" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1367" t="n">
-        <v>458391</v>
+        <v>506429</v>
       </c>
       <c r="C1367" t="n">
+        <v>4.24499988555908</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>4.01000022888184</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>4.10500001907349</v>
+      </c>
+      <c r="G1367" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1368" t="n">
+        <v>415392</v>
+      </c>
+      <c r="C1368" t="n">
+        <v>4.40500020980835</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>4.21500015258789</v>
+      </c>
+      <c r="E1368" t="n">
         <v>4.32999992370605</v>
       </c>
-      <c r="D1367" t="n">
-        <v>4.15999984741211</v>
-      </c>
-      <c r="E1367" t="n">
-        <v>4.16499996185303</v>
-      </c>
-      <c r="F1367" t="n">
-        <v>4.29500007629395</v>
-      </c>
-      <c r="G1367" t="s">
+      <c r="F1368" t="n">
+        <v>4.30499982833862</v>
+      </c>
+      <c r="G1368" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -35977,7 +35977,7 @@
         <v>422900</v>
       </c>
       <c r="C1370" t="n">
-        <v>4.47499990463257</v>
+        <v>4.4850001335144</v>
       </c>
       <c r="D1370" t="n">
         <v>4.32499980926514</v>
@@ -35992,6 +35992,32 @@
         <v>4.4850001335144</v>
       </c>
       <c r="H1370" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>237534</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>4.44500017166138</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>4.44500017166138</v>
+      </c>
+      <c r="H1371" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -36021,6 +36021,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>300124</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>4.32499980926514</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="H1372" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -36047,6 +36047,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>277751</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>4.49499988555908</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>4.30499982833862</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>4.40500020980835</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="H1373" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -36073,6 +36073,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1374">
+      <c r="A1374" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1374" t="n">
+        <v>531143</v>
+      </c>
+      <c r="C1374" t="n">
+        <v>4.6399998664856</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>4.36499977111816</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>4.36499977111816</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>4.6399998664856</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>4.6399998664856</v>
+      </c>
+      <c r="H1374" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -36151,6 +36151,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1377">
+      <c r="A1377" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1377" t="n">
+        <v>452644</v>
+      </c>
+      <c r="C1377" t="n">
+        <v>4.8600001335144</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>4.71500015258789</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>4.77500009536743</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>4.77500009536743</v>
+      </c>
+      <c r="H1377" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -32105,8 +32105,31 @@
       <c r="E1380" t="n">
         <v>4.51000022888184</v>
       </c>
-      <c r="F1380"/>
+      <c r="F1380" t="n">
+        <v>4.54500007629395</v>
+      </c>
       <c r="G1380" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1381" t="n">
+        <v>159356</v>
+      </c>
+      <c r="C1381" t="n">
+        <v>4.72499990463257</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>4.58500003814697</v>
+      </c>
+      <c r="F1381"/>
+      <c r="G1381" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -32128,8 +32128,31 @@
       <c r="E1381" t="n">
         <v>4.58500003814697</v>
       </c>
-      <c r="F1381"/>
+      <c r="F1381" t="n">
+        <v>4.69500017166138</v>
+      </c>
       <c r="G1381" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1382" t="n">
+        <v>230995</v>
+      </c>
+      <c r="C1382" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>4.45499992370605</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F1382"/>
+      <c r="G1382" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -32151,8 +32151,31 @@
       <c r="E1382" t="n">
         <v>4.61999988555908</v>
       </c>
-      <c r="F1382"/>
+      <c r="F1382" t="n">
+        <v>4.50500011444092</v>
+      </c>
       <c r="G1382" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1383" t="n">
+        <v>241102</v>
+      </c>
+      <c r="C1383" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="F1383"/>
+      <c r="G1383" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -32174,8 +32174,31 @@
       <c r="E1383" t="n">
         <v>4.44000005722046</v>
       </c>
-      <c r="F1383"/>
+      <c r="F1383" t="n">
+        <v>4.23999977111816</v>
+      </c>
       <c r="G1383" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1384" t="n">
+        <v>428890</v>
+      </c>
+      <c r="C1384" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>4.31500005722046</v>
+      </c>
+      <c r="F1384"/>
+      <c r="G1384" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -32204,6 +32204,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1385">
+      <c r="A1385" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1385" t="n">
+        <v>271464</v>
+      </c>
+      <c r="C1385" t="n">
+        <v>4.51999998092651</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>4.2649998664856</v>
+      </c>
+      <c r="E1385" t="n">
+        <v>4.44500017166138</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="G1385" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -36437,6 +36437,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1388">
+      <c r="A1388" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1388" t="n">
+        <v>351975</v>
+      </c>
+      <c r="C1388" t="n">
+        <v>4.42500019073486</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E1388" t="n">
+        <v>4.30999994277954</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="H1388" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -36463,6 +36463,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1389">
+      <c r="A1389" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1389" t="n">
+        <v>271428</v>
+      </c>
+      <c r="C1389" t="n">
+        <v>4.46999979019165</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="H1389" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40659,6 +40659,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1390">
+      <c r="A1390" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1390" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1390" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>4.30499982833862</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>222711</v>
+      </c>
+      <c r="I1390" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1391" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1391" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>4.36499977111816</v>
+      </c>
+      <c r="E1391" t="n">
+        <v>4.21000003814697</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>203225</v>
+      </c>
+      <c r="I1391" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40711,9 +40711,38 @@
         <v>4.25</v>
       </c>
       <c r="H1391" t="n">
-        <v>203225</v>
+        <v>204510</v>
       </c>
       <c r="I1391" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1392" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1392" t="n">
+        <v>4.22499990463257</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>4.30000019073486</v>
+      </c>
+      <c r="E1392" t="n">
+        <v>4.22499990463257</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>4.31500005722046</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>4.31500005722046</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>70130</v>
+      </c>
+      <c r="I1392" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40728,7 +40728,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="D1392" t="n">
-        <v>4.30000019073486</v>
+        <v>4.31500005722046</v>
       </c>
       <c r="E1392" t="n">
         <v>4.22499990463257</v>
@@ -40743,6 +40743,35 @@
         <v>70130</v>
       </c>
       <c r="I1392" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1393" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1393" t="n">
+        <v>4.21000003814697</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="E1393" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>4.18499994277954</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>4.18499994277954</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>237299</v>
+      </c>
+      <c r="I1393" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40775,6 +40775,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1394">
+      <c r="A1394" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1394" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1394" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>183400</v>
+      </c>
+      <c r="I1394" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40804,6 +40804,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1395">
+      <c r="A1395" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1395" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1395" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>4.38500022888184</v>
+      </c>
+      <c r="E1395" t="n">
+        <v>4.09999990463257</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>4.35500001907349</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>4.35500001907349</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>136990</v>
+      </c>
+      <c r="I1395" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40833,6 +40833,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1396">
+      <c r="A1396" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1396" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1396" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="H1396" t="n">
+        <v>435216</v>
+      </c>
+      <c r="I1396" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40862,6 +40862,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1397">
+      <c r="A1397" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1397" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1397" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="E1397" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="H1397" t="n">
+        <v>301744</v>
+      </c>
+      <c r="I1397" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40873,7 +40873,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="D1397" t="n">
-        <v>4.65000009536743</v>
+        <v>4.65999984741211</v>
       </c>
       <c r="E1397" t="n">
         <v>4.53999996185303</v>
@@ -40888,6 +40888,35 @@
         <v>301744</v>
       </c>
       <c r="I1397" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1398" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1398" t="n">
+        <v>4.58500003814697</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>4.80000019073486</v>
+      </c>
+      <c r="E1398" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>4.73999977111816</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>4.73999977111816</v>
+      </c>
+      <c r="H1398" t="n">
+        <v>370096</v>
+      </c>
+      <c r="I1398" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IOT.MI.xlsx
+++ b/data/IOT.MI.xlsx
@@ -40920,6 +40920,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1399">
+      <c r="A1399" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1399" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1399" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>4.69500017166138</v>
+      </c>
+      <c r="E1399" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="H1399" t="n">
+        <v>350392</v>
+      </c>
+      <c r="I1399" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
